--- a/output/pdf_financials_xlsx/MFG.xlsx
+++ b/output/pdf_financials_xlsx/MFG.xlsx
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.261852</v>
+        <v>-3.261852</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10.283177</v>
+        <v>-10.283177</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>18.228001</v>
+        <v>-18.228001</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-15.94802</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.261852</v>
+        <v>-3.261852</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.283177</v>
+        <v>-10.283177</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>18.228001</v>
+        <v>-18.228001</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-15.94802</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.261852</v>
+        <v>-3.261852</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>10.283177</v>
+        <v>-10.283177</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>18.228001</v>
+        <v>-18.228001</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-15.94802</v>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>36.2428</v>
+        <v>-36.2428</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>73.45126399999999</v>
+        <v>-73.45126399999999</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>82.85455</v>
+        <v>-82.85455</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>93.811882</v>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.261852</v>
+        <v>-3.261852</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10.283177</v>
+        <v>-10.283177</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>18.228001</v>
+        <v>-18.228001</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-15.94802</v>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.268579</v>
+        <v>-3.255125</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.372387</v>
+        <v>-10.193967</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.378323</v>
+        <v>-18.077679</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-15.869042</v>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.0813</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.636911</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.919581</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.297006</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.660036</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.309124</v>
       </c>
     </row>
     <row r="93">
@@ -4602,7 +4602,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -5168,7 +5172,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5870,7 +5878,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>1.0813</v>
       </c>
@@ -9016,16 +9028,16 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3.261852</v>
+        <v>-3.261852</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>10.283177</v>
+        <v>-10.283177</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>18.228001</v>
+        <v>-18.228001</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>15.94802</v>
+        <v>-15.94802</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MFG.xlsx
+++ b/output/pdf_financials_xlsx/MFG.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000158</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.028643</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.085131</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.332439</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.329989</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.431174</v>
       </c>
     </row>
     <row r="13">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.261852</v>
+        <v>-3.261694</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.283177</v>
+        <v>-10.254534</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-18.228001</v>
+        <v>-18.14287</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-15.94802</v>
+        <v>-16.280459</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-12.682632</v>
+        <v>-13.012621</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.959277999999999</v>
+        <v>-10.390452</v>
       </c>
     </row>
     <row r="28">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.255125</v>
+        <v>-3.254967</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.193967</v>
+        <v>-10.165324</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-18.077679</v>
+        <v>-17.992548</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.869042</v>
+        <v>-16.201481</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-12.682632</v>
+        <v>-13.012621</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.959277999999999</v>
+        <v>-10.390452</v>
       </c>
     </row>
     <row r="30">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.132245</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>12.035601</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.791778</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>13.504009</v>
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.132245</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>12.035601</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.791778</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>13.504009</v>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.158315</v>
+        <v>0.02607</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>12.642582</v>
+        <v>0.606981</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.89934</v>
+        <v>0.107562</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">

--- a/output/pdf_financials_xlsx/MFG.xlsx
+++ b/output/pdf_financials_xlsx/MFG.xlsx
@@ -1135,10 +1135,10 @@
         <v>0.07897800000000001</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.058517</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.030426</v>
       </c>
     </row>
     <row r="29">
@@ -1160,10 +1160,10 @@
         <v>-16.201481</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-13.012621</v>
+        <v>-12.954104</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.390452</v>
+        <v>-10.360026</v>
       </c>
     </row>
     <row r="30">
@@ -2929,15 +2929,11 @@
       <c r="E99" s="3" t="n">
         <v>-15.94802</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-12.682632</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-9.959277999999999</v>
       </c>
     </row>
     <row r="100">
@@ -2958,15 +2954,11 @@
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2987,15 +2979,11 @@
       <c r="E101" s="3" t="n">
         <v>0.115037</v>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>0.080549</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0.036739</v>
       </c>
     </row>
     <row r="102">
@@ -3016,15 +3004,11 @@
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3045,15 +3029,11 @@
       <c r="E103" s="3" t="n">
         <v>-0.142249</v>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>-0.104885</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>-0.182516</v>
       </c>
     </row>
     <row r="104">
@@ -3074,15 +3054,11 @@
       <c r="E104" s="3" t="n">
         <v>-0.685972</v>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>-0.530528</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.417662</v>
       </c>
     </row>
     <row r="105">
@@ -3103,15 +3079,11 @@
       <c r="E105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3132,15 +3104,11 @@
       <c r="E106" s="3" t="n">
         <v>-0.713184</v>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>-0.554864</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.271885</v>
       </c>
     </row>
     <row r="107">
@@ -3150,26 +3118,22 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>1.0813</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.555611</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>3.28267</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.618282</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>2.029574</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0.815478</v>
       </c>
     </row>
     <row r="108">
@@ -3190,15 +3154,11 @@
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3219,15 +3179,11 @@
       <c r="E109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3248,15 +3204,11 @@
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3277,15 +3229,11 @@
       <c r="E111" s="3" t="n">
         <v>-0.025504</v>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>-0.000221</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>-0.008302</v>
       </c>
     </row>
     <row r="112">
@@ -3306,15 +3254,11 @@
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3335,15 +3279,11 @@
       <c r="E113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3364,15 +3304,11 @@
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3393,15 +3329,11 @@
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3422,15 +3354,11 @@
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3451,15 +3379,11 @@
       <c r="E117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3480,15 +3404,11 @@
       <c r="E118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3509,15 +3429,11 @@
       <c r="E119" s="3" t="n">
         <v>-0.025504</v>
       </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F119" s="3" t="n">
+        <v>-0.000221</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0.035342</v>
       </c>
     </row>
     <row r="120">
@@ -3536,17 +3452,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.352183</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>5.876461</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>37.397181</v>
       </c>
     </row>
     <row r="121">
@@ -3567,15 +3479,11 @@
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3596,15 +3504,11 @@
       <c r="E122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3625,15 +3529,11 @@
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3654,15 +3554,11 @@
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3683,15 +3579,11 @@
       <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3712,15 +3604,11 @@
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3776,17 +3664,13 @@
         <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.135539</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>-0.135539</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3807,15 +3691,11 @@
       <c r="E129" s="3" t="n">
         <v>23.505921</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>9.868137000000001</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>37.509685</v>
       </c>
     </row>
     <row r="130">
@@ -3836,15 +3716,11 @@
       <c r="E130" s="3" t="n">
         <v>6.791778</v>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="3" t="n">
+        <v>13.504009</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>9.534129</v>
       </c>
     </row>
     <row r="131">
@@ -3865,15 +3741,11 @@
       <c r="E131" s="3" t="n">
         <v>-0.009682</v>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3894,15 +3766,11 @@
       <c r="E132" s="3" t="n">
         <v>6.712231</v>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>-3.96988</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>28.659854</v>
       </c>
     </row>
     <row r="133">
@@ -3923,15 +3791,11 @@
       <c r="E133" s="3" t="n">
         <v>13.504009</v>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>9.534129</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>38.193983</v>
       </c>
     </row>
     <row r="134">
@@ -3952,15 +3816,11 @@
       <c r="E134" s="3" t="n">
         <v>-0.025504</v>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>-0.000221</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>-0.008302</v>
       </c>
     </row>
     <row r="135">
@@ -3981,15 +3841,11 @@
       <c r="E135" s="3" t="n">
         <v>-16.784008</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>-13.838017</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-8.897364</v>
       </c>
     </row>
   </sheetData>
@@ -4003,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6400,12 +6256,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6413,27 +6269,31 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>-3.261852</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>-10.283177</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-18.228001</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>-15.94802</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-12.682632</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-9.959277999999999</v>
       </c>
     </row>
     <row r="54">
@@ -6444,15 +6304,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6463,21 +6327,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.006365</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.009682</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07897800000000001</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.058517</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.030426</v>
       </c>
     </row>
     <row r="55">
@@ -6488,40 +6350,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0.006727</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.08921</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.150322</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.07897800000000001</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.505617</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.607048</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.815478</v>
       </c>
     </row>
     <row r="56">
@@ -6532,12 +6396,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Other income - flow-through premium</t>
+          <t>Amortization of flow-through premium liability</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -6546,19 +6410,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>-2.592992</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-3.024191</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H56" s="5" t="n">
         <v>-2.691577</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="5" t="n">
+        <v>-1.27911</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -6574,36 +6440,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Share-based payment expense</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>1.0813</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0.555611</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>3.28267</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>2.505617</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.013245</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.003929</v>
       </c>
     </row>
     <row r="58">
@@ -6614,40 +6484,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>-0.015094</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.168172</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.21602</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0.115037</v>
+          <t>Interest income on GIC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J58" s="5" t="n">
+        <v>-0.043644</v>
       </c>
     </row>
     <row r="59">
@@ -6658,40 +6530,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>-0.02607</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.580911</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.499419</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>-0.142249</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.115037</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.080549</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.036739</v>
       </c>
     </row>
     <row r="60">
@@ -6702,40 +6576,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0.590568</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.421388</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>1.195226</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>-0.685972</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.142249</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>-0.104885</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-0.182516</v>
       </c>
     </row>
     <row r="61">
@@ -6746,40 +6622,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>-1.085179</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>-12.555938</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-16.34694</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>-16.758504</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.685972</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>-0.530528</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>0.417662</v>
       </c>
     </row>
     <row r="62">
@@ -6790,40 +6668,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment 4</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-0.366803</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.186017</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.116426</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>-0.025504</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.758504</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>-13.837796</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-8.889061999999999</v>
       </c>
     </row>
     <row r="63">
@@ -6834,40 +6714,46 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Purchase of short-term investment</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>-14.364303</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.186017</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.116426</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>-0.025504</v>
+          <t>PurchaseOfShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J63" s="5" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="64">
@@ -6878,36 +6764,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Issuance of shares - private placements proceeds, net of costs 8 (ii)</t>
+          <t>Maturity of short-term investment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>18.120968</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>22.667688</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>11.272045</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>23.352183</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J64" s="5" t="n">
+        <v>3.043644</v>
       </c>
     </row>
     <row r="65">
@@ -6918,15 +6810,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Proceeds from option exercises</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Purchases of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6943,17 +6839,13 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.163704</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025504</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-0.000221</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-0.008302</v>
       </c>
     </row>
     <row r="66">
@@ -6964,38 +6856,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Payment of lease liability 5</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Cash provided by (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.019272</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.058867</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>-0.009965999999999999</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.000221</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0.035342</v>
       </c>
     </row>
     <row r="67">
@@ -7006,40 +6904,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cash from financing activities</t>
+          <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>18.120968</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>22.648416</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>11.213178</v>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>23.505921</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.352183</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>5.876461</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>37.397181</v>
       </c>
     </row>
     <row r="68">
@@ -7050,40 +6950,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange rate changes on cash</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>-0.539242</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>-0.003105</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.006365</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>-0.009682</v>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J68" s="5" t="n">
+        <v>0.112504</v>
       </c>
     </row>
     <row r="69">
@@ -7094,17 +6996,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash</t>
+          <t>Proceeds from exercise of options</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7117,16 +7019,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>-5.243823</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>6.712231</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.163704</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>3.991676</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -7142,40 +7044,42 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>2.132245</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>12.035601</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>6.791778</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.505921</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>9.868137000000001</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>37.509685</v>
       </c>
     </row>
     <row r="71">
@@ -7186,40 +7090,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>2.132245</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>12.035601</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>6.791778</v>
+          <t>Effect of exchange rate on changes in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>13.504009</v>
+        <v>-0.009682</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J71" s="5" t="n">
+        <v>0.003889</v>
       </c>
     </row>
     <row r="72">
@@ -7230,15 +7134,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fair value reversal of exercise of options 8 (iii) $</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7255,17 +7163,13 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.128192</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.712231</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>-3.96988</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>28.659854</v>
       </c>
     </row>
     <row r="73">
@@ -7276,38 +7180,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.   NATURE OF OPERATIONS</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbia Business Corporation Act. The address of the Company’s registered and records office is Suite</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0.0007</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.791778</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>13.504009</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>9.534129</v>
       </c>
     </row>
     <row r="74">
@@ -7318,40 +7226,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.003105</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-0.006365</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>13.504009</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>9.534129</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>38.193983</v>
       </c>
     </row>
     <row r="75">
@@ -7362,44 +7272,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net (decrease) increase in cash</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash interest income received</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>9.903356</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-5.243823</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.332439</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.329989</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.122244</v>
       </c>
     </row>
     <row r="76">
@@ -7410,35 +7314,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Fair value reversal on exercise of options</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0.539242</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.003105</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>0.128192</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>3.244018</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -7454,17 +7358,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cash held in trust for asset acquisition 6</t>
+          <t>Finders’ warrants issued</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>-13.9975</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7486,10 +7392,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J77" s="5" t="n">
+        <v>0.877484</v>
       </c>
     </row>
     <row r="78">
@@ -7500,12 +7404,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Payment of lease liability</t>
+          <t>Interest paid in cash</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7514,8 +7418,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>-0.019272</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -7546,24 +7452,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net increase in cash</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>2.132244</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>9.903356</v>
+          <t>Income tax paid in cash</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7589,24 +7495,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2023 50,156,064 66,493,689 7,297,006</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7628,26 +7530,26 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.058517</v>
+        <v>25.94686</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>0.030426</v>
+        <v>-47.843835</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 9, 13</t>
+          <t>Issuance of common shares - private placements 1,670,000 6,012,000 -</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -7672,33 +7574,31 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>8.416123000000001</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>7.32265</v>
+        <v>6.012</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>General and administrative 12, 13</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share issue costs - (135,539) -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7720,26 +7620,28 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>5.326798</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>2.290927</v>
+        <v>-0.135539</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Share-based payments 11, 13</t>
+          <t>Issuance of common shares - exercise of options 2,815,450 3,991,676 -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -7764,33 +7666,31 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>0.607048</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>0.815478</v>
+        <v>3.991676</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Fair value of share options exercised from share-based payments reserve - 3,244,018 (3,244,018)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7811,30 +7711,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n">
-        <v>14.408486</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>10.459481</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 10</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Share-based payments - - 607,048</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7850,13 +7758,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>0.607048</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>1.27911</v>
+        <v>0.607048</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -7867,22 +7773,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Loss and comprehensive loss - - -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7900,39 +7806,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>-15.94802</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.013245</v>
+        <v>-12.682632</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>0.003929</v>
+        <v>-12.682632</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Interest income 5, 6</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2024 54,641,514 79,605,844 4,660,036</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7954,33 +7854,29 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.329989</v>
+        <v>23.739413</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0.431174</v>
+        <v>-60.526467</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Issuance of common shares - private placement 12,122,002 40,002,600 -</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -8002,33 +7898,31 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>0.06510000000000001</v>
+        <v>40.0026</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs - (3,482,903) 877,484</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -8050,33 +7944,31 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-12.682632</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-9.959277999999999</v>
+        <v>-2.605419</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 1)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 34,092 156,378 (43,874)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -8098,29 +7990,35 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-2.4e-07</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>0.112504</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 1)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Share-based payments - - 815,478</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8142,33 +8040,31 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>52.103344</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>58.199</v>
+        <v>0.815478</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2025 66,797,608 116,281,919 6,309,124</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -8184,35 +8080,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n">
-        <v>0.07897800000000001</v>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.058517</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>52.105298</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-70.48574499999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 8, 12</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -8229,10 +8129,10 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>13.703003</v>
+        <v>-15.94802</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>8.416123000000001</v>
+        <v>-12.682632</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -8243,24 +8143,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>General and administrative 11, 12</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8277,10 +8173,10 @@
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>2.804756</v>
+        <v>0.009682</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>5.326798</v>
+        <v>0.013245</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -8291,20 +8187,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share-based payments 10, 12</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8321,10 +8221,10 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>2.505617</v>
+        <v>-0.025504</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.607048</v>
+        <v>-0.000221</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -8335,17 +8235,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 9</t>
+          <t>Payment of lease liability</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -8365,10 +8265,12 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>2.691577</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>1.27911</v>
+        <v>-0.009965999999999999</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -8379,24 +8281,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Income taxes paid in cash</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8412,11 +8310,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n">
-        <v>-0.009682</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>-0.013245</v>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -8427,24 +8329,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Interest income 5</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2022 87,951,007 46,277,610 4,919,581</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8461,10 +8359,10 @@
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.332439</v>
+        <v>19.301376</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.329989</v>
+        <v>-31.895815</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -8475,24 +8373,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Other income 12</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Issuance of common shares - private placements 12,070,000 24,525,050 -</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8509,10 +8403,12 @@
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>0.13</v>
+        <v>24.52505</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -8523,24 +8419,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Flow-through premium - private placements</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8557,10 +8449,10 @@
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-15.94802</v>
+        <v>-3.428</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-12.682632</v>
+        <v>-3.428</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -8571,24 +8463,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share issue costs - (1,172,867) -</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8605,10 +8493,12 @@
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-1.7e-07</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>-1.2e-07</v>
+        <v>-1.172867</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -8619,17 +8509,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Issuance of common shares - exercise of options 291,100 163,704 -</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8649,10 +8539,12 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>94.268443</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>104.206688</v>
+        <v>0.163704</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -8663,31 +8555,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 11 $</t>
+          <t>Fair value of share options exercised from share-based payments reserve - 128,192 (128,192)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>0.421202</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>9.787283</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>15.750956</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>13.703003</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -8703,35 +8603,41 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>General and administrative expenses 12</t>
+          <t>Share-based payments - - 2,505,617</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>1.213539</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>2.469603</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>2.20674</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>2.804756</v>
+        <v>2.505617</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8747,36 +8653,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8</t>
+          <t>Balance, December 31, 2023 100,312,107 66,493,689 7,297,006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>1.0813</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.555611</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>3.28267</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>2.505617</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.94686</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>-47.843835</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -8787,31 +8697,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Depreciation expense 4</t>
+          <t>Issuance of common shares - private placements 3,340,000 6,012,000 -</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" s="5" t="n">
-        <v>0.006727</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>0.08921</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0.150322</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.07897800000000001</v>
+        <v>6.012</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -8827,22 +8743,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Share issue costs -</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8855,16 +8771,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="5" t="n">
-        <v>-0.006365</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.009682</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.135539</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>-0.135539</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -8875,35 +8791,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>-0.000158</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.028643</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>-0.085131</v>
+          <t>Issuance of common shares - exercise of options 5,630,900 3,991,676 -</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>-0.332439</v>
+        <v>3.991676</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -8919,24 +8837,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Other income 9</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2024 109,283,007 79,605,844 4,660,036</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -8947,16 +8861,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" s="5" t="n">
-        <v>-0.047</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.739413</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>-60.526467</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -8967,33 +8881,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other income - flow through premium 7</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-3.261852</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>-2.592992</v>
+        <v>-10.283177</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-3.024191</v>
+        <v>-18.228001</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>-2.691577</v>
+        <v>-15.94802</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9009,35 +8925,35 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>-3.261852</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>-10.283177</v>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-18.228001</v>
+        <v>-0.006365</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>-15.94802</v>
+        <v>0.009682</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9053,35 +8969,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>9e-08</v>
+        <v>0.006727</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>1.4e-07</v>
+        <v>0.08921</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2.2e-07</v>
+        <v>0.150322</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>1.7e-07</v>
+        <v>0.07897800000000001</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -9097,17 +9013,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Other income - flow-through premium</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -9116,16 +9032,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="5" t="n">
+        <v>-2.592992</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>82.91730800000001</v>
+        <v>-3.024191</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>94.268443</v>
+        <v>-2.691577</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -9141,35 +9055,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2022 80,651,007 $ 37,364,565 $ 1,636,911 $</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based payment expense</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>1.0813</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.555611</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>25.333662</v>
+        <v>3.28267</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>-13.667814</v>
+        <v>2.505617</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -9185,37 +9099,35 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Issuance of common shares - private placements 8 (ii) 7,300,000 11,989,000 -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>-0.015094</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>-0.168172</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>11.989</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.21602</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.115037</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -9231,37 +9143,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Flow-through premium - private placements 8 (ii) - (2,359,000) -</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>-0.02607</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>-0.580911</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>-2.359</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.499419</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-0.142249</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -9277,37 +9187,35 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Share issue costs 8 (ii) - (716,955) -</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.590568</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.421388</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>-0.716955</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.195226</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>-0.685972</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -9323,37 +9231,35 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8 (iii) - - 3,282,670</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>-1.085179</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>-12.555938</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>3.28267</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.34694</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>-16.758504</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -9369,39 +9275,35 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - -</t>
+          <t>Acquisition of property, plant and equipment 4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>-0.366803</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>-0.186017</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>-18.228001</v>
+        <v>-0.116426</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>-18.228001</v>
+        <v>-0.025504</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -9417,35 +9319,35 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 87,951,007 46,277,610 4,919,581</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-14.364303</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-0.186017</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>19.301376</v>
+        <v>-0.116426</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>-31.895815</v>
+        <v>-0.025504</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -9461,37 +9363,31 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Issuance of common shares - private placements 8 (ii) 12,070,000 24,525,050 -</t>
+          <t>Issuance of shares - private placements proceeds, net of costs 8 (ii)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="5" t="n">
+        <v>18.120968</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>22.667688</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>24.52505</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.272045</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>23.352183</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -9507,17 +9403,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Flow-through premium - private placements 8 (ii) - (3,428,000) -</t>
+          <t>Proceeds from option exercises</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9531,13 +9427,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>-3.428</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0.163704</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9553,17 +9449,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Share issue costs 8 (ii) - (1,172,867) -</t>
+          <t>Payment of lease liability 5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9572,18 +9468,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="5" t="n">
+        <v>-0.019272</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>-1.172867</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.058867</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>-0.009965999999999999</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9599,37 +9491,35 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Issuance of common shares - exercise of options 8 (iii) 291,100 163,704 -</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>18.120968</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>22.648416</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.163704</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.213178</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>23.505921</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9645,39 +9535,35 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fair value of share options exercised from share-based payments reserve 8 (iii) - 128,192 (128,192)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Effect of foreign exchange rate changes on cash</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>-0.539242</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-0.003105</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.006365</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-0.009682</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -9693,20 +9579,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8 (iii) - - 2,505,617</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Net increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -9718,12 +9608,10 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2.505617</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.243823</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>6.712231</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9739,35 +9627,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 100,312,107 $ 66,493,689 $ 7,297,006 $</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>2.132245</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>25.94686</v>
+        <v>12.035601</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>-47.843835</v>
+        <v>6.791778</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9783,39 +9671,35 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>2.132245</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.003105</v>
+        <v>12.035601</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>-0.006365</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.791778</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>13.504009</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -9831,33 +9715,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Fair value reversal of exercise of options 8 (iii) $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>36.914603</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>75.09542399999999</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>82.91730800000001</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.128192</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -9873,17 +9761,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>1.   NATURE OF OPERATIONS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2021 67,511,485 $ 18,494,747 $ 1,081,300 $</t>
+          <t>Columbia Business Corporation Act. The address of the Company’s registered and records office is Suite</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9893,15 +9781,13 @@
         </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>16.19141</v>
+        <v>0.0007</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>-3.384637</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0007</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.0007</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -9917,30 +9803,30 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Issuance of common shares - in kind for services 8 (ii) 1,622 3,000 -</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>0.003</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003105</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>-0.006365</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -9961,30 +9847,34 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Issuance of common shares - private placements 8 (ii) 13,137,900 24,417,985 -</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>24.417985</v>
+          <t>Net (decrease) increase in cash</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>24.417985</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.903356</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>-5.243823</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -10005,25 +9895,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Flow-through premium - private placements 8 (ii) - (3,800,870) -</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" s="5" t="n">
-        <v>-3.80087</v>
+        <v>0.539242</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>-3.80087</v>
+        <v>0.003105</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -10049,27 +9939,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Share issue costs 8 (ii) - (1,750,297) -</t>
+          <t>Cash held in trust for asset acquisition 6</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>-1.750297</v>
+      <c r="E134" s="5" t="n">
+        <v>-13.9975</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -10095,25 +9985,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8 (iii) - - 555,611</t>
+          <t>Payment of lease liability</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>0.555611</v>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.555611</v>
+        <v>-0.019272</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10139,32 +10031,34 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - -</t>
+          <t>Net increase in cash</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>-3.261852</v>
+        <v>2.132244</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-10.283177</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>-10.283177</v>
+        <v>9.903356</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10190,40 +10084,44 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 80,651,007 37,364,565 1,636,911</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Depreciation 8</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>25.333662</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>-13.667814</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="5" t="n">
+        <v>0.058517</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>0.030426</v>
       </c>
     </row>
     <row r="138">
@@ -10234,12 +10132,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Issuance of common shares - private placements 8 (ii) 7,300,000 11,989,000 -</t>
+          <t>Exploration and evaluation 9, 13</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -10248,8 +10146,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>11.989</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -10261,15 +10161,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="5" t="n">
+        <v>8.416123000000001</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>7.32265</v>
       </c>
     </row>
     <row r="139">
@@ -10280,22 +10176,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Flow-through premium - private placements 8 (ii) - (2,359,000) -</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>General and administrative 12, 13</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F139" s="5" t="n">
-        <v>-2.359</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -10307,15 +10209,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I139" s="5" t="n">
+        <v>5.326798</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>2.290927</v>
       </c>
     </row>
     <row r="140">
@@ -10326,12 +10224,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Share issue costs 8 (ii) - (716,955) -</t>
+          <t>Share-based payments 11, 13</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -10340,8 +10238,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>-0.716955</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -10353,15 +10253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="5" t="n">
+        <v>0.607048</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>0.815478</v>
       </c>
     </row>
     <row r="141">
@@ -10372,22 +10268,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8 (iii) - - 3,282,670</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>3.28267</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -10399,15 +10301,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="5" t="n">
+        <v>14.408486</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>10.459481</v>
       </c>
     </row>
     <row r="142">
@@ -10418,12 +10316,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 87,951,007 $ 46,277,610 $ 4,919,581 $</t>
+          <t>Amortization of flow-through premium liability 10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10432,21 +10330,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>19.301376</v>
-      </c>
-      <c r="G142" s="5" t="n">
-        <v>-31.895815</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I142" s="5" t="n">
+        <v>1.27911</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -10462,12 +10362,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10475,11 +10375,15 @@
           <t>OtherIncomeExpense</t>
         </is>
       </c>
-      <c r="E143" s="5" t="n">
-        <v>0.539242</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>0.003105</v>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -10491,15 +10395,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I143" s="5" t="n">
+        <v>-0.013245</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>0.003929</v>
       </c>
     </row>
     <row r="144">
@@ -10510,22 +10410,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Other income - flow through shares 7</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Interest income 5, 6</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n">
-        <v>-2.592992</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -10537,15 +10443,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I144" s="5" t="n">
+        <v>0.329989</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>0.431174</v>
       </c>
     </row>
     <row r="145">
@@ -10556,20 +10458,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2020 1 $ 1 $ - $</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>-0.122784</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>-0.122785</v>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -10581,15 +10491,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -10600,17 +10506,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Issuance of common shares - in kind for services 8 (ii) 21,481,704 373,778 -</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>0.373778</v>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -10627,15 +10539,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I146" s="5" t="n">
+        <v>-12.682632</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>-9.959277999999999</v>
       </c>
     </row>
     <row r="147">
@@ -10646,17 +10554,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Issuance of common shares - founders' shares 8 (ii) 5,000,000 50,000 -</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>0.05</v>
+          <t>Basic and diluted (Note 1)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -10673,15 +10587,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="5" t="n">
+        <v>-2.4e-07</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
     </row>
     <row r="148">
@@ -10692,17 +10602,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Issuance of common shares - private placement 8 (ii) 41,029,780 18,299,996 -</t>
+          <t>Basic and diluted (Note 1)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>18.299996</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -10719,15 +10631,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I148" s="5" t="n">
+        <v>52.103344</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>58.199</v>
       </c>
     </row>
     <row r="149">
@@ -10738,17 +10646,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Share issue costs - (229,028) -</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" s="5" t="n">
-        <v>-0.229028</v>
+          <t>Depreciation 7</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -10760,15 +10674,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H149" s="5" t="n">
+        <v>0.07897800000000001</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>0.058517</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -10784,17 +10694,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Share-based payment expense 8 (iii) - - 1,081,300</t>
+          <t>Exploration and evaluation 8, 12</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>1.0813</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -10806,15 +10718,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>13.703003</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>8.416123000000001</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -10830,35 +10738,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 67,511,485 18,494,747 1,081,300</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>16.19141</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>-3.384637</v>
+          <t>General and administrative 11, 12</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H151" s="5" t="n">
+        <v>2.804756</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>5.326798</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -10874,17 +10786,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Share issue costs - (1,750,297) -</t>
+          <t>Share-based payments 10, 12</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" s="5" t="n">
-        <v>-1.750297</v>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -10896,15 +10810,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H152" s="5" t="n">
+        <v>2.505617</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>0.607048</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -10920,37 +10830,2617 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Amortization of flow-through premium liability 9</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>2.691577</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>1.27911</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-0.009682</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>-0.013245</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Interest income 5</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.332439</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>0.329989</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Other income 12</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>-15.94802</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>-12.682632</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>-1.7e-07</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>-1.2e-07</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>94.268443</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>104.206688</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenses 11 $</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>0.421202</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>9.787283</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>15.750956</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>13.703003</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>General and administrative expenses 12</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>1.213539</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>2.469603</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>2.20674</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>2.804756</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" s="5" t="n">
+        <v>1.0813</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.555611</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>3.28267</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>2.505617</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Depreciation expense 4</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>0.006727</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.150322</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.07897800000000001</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>-0.006365</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.009682</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>-0.000158</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>-0.028643</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>-0.085131</v>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>-0.332439</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Other income 9</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Other income - flow through premium 7</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>-2.592992</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>-3.024191</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>-2.691577</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>-3.261852</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>-10.283177</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>-18.228001</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-15.94802</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>1.4e-07</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>2.2e-07</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>1.7e-07</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>82.91730800000001</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>94.268443</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2022 80,651,007 $ 37,364,565 $ 1,636,911 $</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>25.333662</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>-13.667814</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - private placements 8 (ii) 7,300,000 11,989,000 -</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Flow-through premium - private placements 8 (ii) - (2,359,000) -</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-2.359</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Share issue costs 8 (ii) - (716,955) -</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>-0.716955</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8 (iii) - - 3,282,670</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>3.28267</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>-18.228001</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>-18.228001</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 87,951,007 46,277,610 4,919,581</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>19.301376</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>-31.895815</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - private placements 8 (ii) 12,070,000 24,525,050 -</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>24.52505</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Flow-through premium - private placements 8 (ii) - (3,428,000) -</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>-3.428</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Share issue costs 8 (ii) - (1,172,867) -</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-1.172867</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - exercise of options 8 (iii) 291,100 163,704 -</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.163704</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Fair value of share options exercised from share-based payments reserve 8 (iii) - 128,192 (128,192)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8 (iii) - - 2,505,617</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>2.505617</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Notes    shares     Share capital       reserve           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 100,312,107 $ 66,493,689 $ 7,297,006 $</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>25.94686</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>-47.843835</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>0.003105</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>-0.006365</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" s="5" t="n">
+        <v>36.914603</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>75.09542399999999</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>82.91730800000001</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2021 67,511,485 $ 18,494,747 $ 1,081,300 $</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>16.19141</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>-3.384637</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - in kind for services 8 (ii) 1,622 3,000 -</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - private placements 8 (ii) 13,137,900 24,417,985 -</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
+        <v>24.417985</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>24.417985</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Flow-through premium - private placements 8 (ii) - (3,800,870) -</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>-3.80087</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>-3.80087</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Share issue costs 8 (ii) - (1,750,297) -</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>-1.750297</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8 (iii) - - 555,611</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
+        <v>0.555611</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>0.555611</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>-3.261852</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>-10.283177</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>-10.283177</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 80,651,007 37,364,565 1,636,911</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>25.333662</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>-13.667814</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - private placements 8 (ii) 7,300,000 11,989,000 -</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Flow-through premium - private placements 8 (ii) - (2,359,000) -</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-2.359</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Share issue costs 8 (ii) - (716,955) -</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>-0.716955</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8 (iii) - - 3,282,670</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>3.28267</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 87,951,007 $ 46,277,610 $ 4,919,581 $</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>19.301376</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>-31.895815</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>0.539242</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>0.003105</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Other income - flow through shares 7</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>-2.592992</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2020 1 $ 1 $ - $</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>-0.122784</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>-0.122785</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - in kind for services 8 (ii) 21,481,704 373,778 -</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>0.373778</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - founders' shares 8 (ii) 5,000,000 50,000 -</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Issuance of common shares - private placement 8 (ii) 41,029,780 18,299,996 -</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>18.299996</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Share issue costs - (229,028) -</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>-0.229028</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 8 (iii) - - 1,081,300</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>1.0813</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2020 67,511,485 18,494,747 1,081,300</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>16.19141</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>-3.384637</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Share issue costs - (1,750,297) -</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>-1.750297</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Notes      shares       Share capital       reserve            Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Balance, December 31, 2021 80,651,007 $ 37,364,565 $ 1,636,911 $</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="n">
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
         <v>25.333662</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F210" s="5" t="n">
         <v>-13.667814</v>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
